--- a/data/publications/handbook-statistics-on-indian-economy/annual-series/national-income-saving-employment/Employment in Public and Organised Private Sectors.xlsx
+++ b/data/publications/handbook-statistics-on-indian-economy/annual-series/national-income-saving-employment/Employment in Public and Organised Private Sectors.xlsx
@@ -374,12 +374,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D63"/>
+  <dimension ref="A1:E64"/>
   <cols>
     <col min="1" max="1" width="4.67767866666667" customWidth="1"/>
     <col min="2" max="2" width="15.4582386666667" customWidth="1"/>
     <col min="3" max="4" width="20.8466173333333" customWidth="1"/>
     <col min="5" max="5" width="20.85042" customWidth="1"/>
+    <col min="6" max="6" width="4.67767866666667" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="28.7982" customHeight="1"/>
@@ -1191,6 +1192,7 @@
       <c r="D63" s="11"/>
       <c r="E63" s="11"/>
     </row>
+    <row r="64" s="1" customFormat="1" ht="28.7982" customHeight="1"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="B2:E2"/>
